--- a/projects/yiwu_weichuang/data/keywords/yiwu_weichuang.xlsx
+++ b/projects/yiwu_weichuang/data/keywords/yiwu_weichuang.xlsx
@@ -32,289 +32,289 @@
     <t>keyword</t>
   </si>
   <si>
-    <t>义乌义城医院怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院靠谱吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院评价</t>
-  </si>
-  <si>
-    <t>义乌义城医院好不好</t>
-  </si>
-  <si>
-    <t>义乌义城医院正规吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院值得去吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院能不能去</t>
-  </si>
-  <si>
-    <t>义乌义城医院有没有坑</t>
-  </si>
-  <si>
-    <t>义乌义城医院真实情况</t>
-  </si>
-  <si>
-    <t>义乌义城医院口碑怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院收费高吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院贵不贵</t>
-  </si>
-  <si>
-    <t>义乌义城医院价格怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院乱收费吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院费用情况</t>
-  </si>
-  <si>
-    <t>义乌义城医院医生怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院医生靠谱吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院医生水平</t>
-  </si>
-  <si>
-    <t>义乌义城医院技术怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院专业吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院环境怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院服务怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院体验如何</t>
-  </si>
-  <si>
-    <t>义乌义城医院看病流程</t>
-  </si>
-  <si>
-    <t>义乌义城医院检查怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院真实评价</t>
-  </si>
-  <si>
-    <t>义乌义城医院网友评价</t>
-  </si>
-  <si>
-    <t>义乌义城医院有人去过吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院反馈如何</t>
-  </si>
-  <si>
-    <t>义乌义城医院看皮肤科怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院皮肤科靠谱吗</t>
-  </si>
-  <si>
-    <t>义乌皮肤科医院怎么选</t>
-  </si>
-  <si>
-    <t>在义乌看皮肤科去哪家好</t>
-  </si>
-  <si>
-    <t>义乌皮肤科医院怎么选比较好</t>
-  </si>
-  <si>
-    <t>私立医院靠谱吗皮肤科</t>
-  </si>
-  <si>
-    <t>私立医院和公立医院哪个好皮肤科</t>
-  </si>
-  <si>
-    <t>义乌义城治疗安全吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院检查贵吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院会不会被坑</t>
-  </si>
-  <si>
-    <t>义乌义城医院可信吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院是正规的吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院安全吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院效果怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院治疗靠谱吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院口碑好吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院评价真实吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院到底怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院真实口碑</t>
-  </si>
-  <si>
-    <t>义乌义城医院评价到底怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院看病靠谱吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院可信吗知乎</t>
-  </si>
-  <si>
-    <t>义乌义城医院有没有去过的</t>
-  </si>
-  <si>
-    <t>义乌义城医院怎么样真实反馈</t>
-  </si>
-  <si>
-    <t>义乌义城医院评价好不好</t>
-  </si>
-  <si>
-    <t>义乌义城医院靠谱吗真实经历</t>
-  </si>
-  <si>
-    <t>义乌义城医院到底好不好</t>
-  </si>
-  <si>
-    <t>义乌义城医院情况怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院收费情况如何</t>
-  </si>
-  <si>
-    <t>义乌义城医院费用贵不贵</t>
-  </si>
-  <si>
-    <t>义乌义城医院价格高不高</t>
-  </si>
-  <si>
-    <t>义乌义城医院收费合理吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院检查费用怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院医生靠谱吗知乎</t>
-  </si>
-  <si>
-    <t>义乌义城医院医生评价如何</t>
-  </si>
-  <si>
-    <t>义乌义城医院医生水平怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院医生好不好</t>
-  </si>
-  <si>
-    <t>义乌义城医院技术靠谱吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院服务好不好</t>
-  </si>
-  <si>
-    <t>义乌义城医院体验怎么样知乎</t>
-  </si>
-  <si>
-    <t>义乌义城医院环境好不好</t>
-  </si>
-  <si>
-    <t>义乌义城医院就诊体验如何</t>
-  </si>
-  <si>
-    <t>义乌义城医院看病流程复杂吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院是不是正规的吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院是不是私立医院</t>
-  </si>
-  <si>
-    <t>义乌义城医院资质怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院靠谱吗安全吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院看皮肤科靠谱吗</t>
-  </si>
-  <si>
-    <t>义乌义城医院皮肤科评价怎么样</t>
-  </si>
-  <si>
-    <t>义乌义城医院皮肤科好不好</t>
-  </si>
-  <si>
-    <t>义乌义城医院皮肤科怎么样真实情况</t>
-  </si>
-  <si>
-    <t>义乌哪家皮肤科医院比较靠谱</t>
-  </si>
-  <si>
-    <t>义乌皮肤科医院哪家评价好</t>
-  </si>
-  <si>
-    <t>义乌皮肤科医院哪个好一点</t>
-  </si>
-  <si>
-    <t>义乌看皮肤科医院怎么选</t>
-  </si>
-  <si>
-    <t>义乌皮肤科医院收费情况</t>
-  </si>
-  <si>
-    <t>私立皮肤科医院靠谱吗义乌</t>
+    <t>义乌微创医院怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院靠谱吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院评价</t>
+  </si>
+  <si>
+    <t>义乌微创医院好不好</t>
+  </si>
+  <si>
+    <t>义乌微创医院正规吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院值得去吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院能不能去</t>
+  </si>
+  <si>
+    <t>义乌微创医院有没有坑</t>
+  </si>
+  <si>
+    <t>义乌微创医院真实情况</t>
+  </si>
+  <si>
+    <t>义乌微创医院口碑怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院收费高吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院贵不贵</t>
+  </si>
+  <si>
+    <t>义乌微创医院价格怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院乱收费吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院费用情况</t>
+  </si>
+  <si>
+    <t>义乌微创医院医生怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院医生靠谱吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院医生水平</t>
+  </si>
+  <si>
+    <t>义乌微创医院技术怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院专业吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院环境怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院服务怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院体验如何</t>
+  </si>
+  <si>
+    <t>义乌微创医院看病流程</t>
+  </si>
+  <si>
+    <t>义乌微创医院检查怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院真实评价</t>
+  </si>
+  <si>
+    <t>义乌微创医院网友评价</t>
+  </si>
+  <si>
+    <t>义乌微创医院有人去过吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院反馈如何</t>
+  </si>
+  <si>
+    <t>义乌微创医院看妇科怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院妇科靠谱吗</t>
+  </si>
+  <si>
+    <t>义乌妇科医院怎么选</t>
+  </si>
+  <si>
+    <t>在义乌看妇科去哪家好</t>
+  </si>
+  <si>
+    <t>义乌妇科医院怎么选比较好</t>
+  </si>
+  <si>
+    <t>私立医院靠谱吗妇科</t>
+  </si>
+  <si>
+    <t>私立医院和公立医院哪个好妇科</t>
+  </si>
+  <si>
+    <t>义乌微创治疗安全吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院检查贵吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院会不会被坑</t>
+  </si>
+  <si>
+    <t>义乌微创医院可信吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院是正规的吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院安全吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院效果怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院治疗靠谱吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院口碑好吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院评价真实吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院到底怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院真实口碑</t>
+  </si>
+  <si>
+    <t>义乌微创医院评价到底怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院看病靠谱吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院可信吗知乎</t>
+  </si>
+  <si>
+    <t>义乌微创医院有没有去过的</t>
+  </si>
+  <si>
+    <t>义乌微创医院怎么样真实反馈</t>
+  </si>
+  <si>
+    <t>义乌微创医院评价好不好</t>
+  </si>
+  <si>
+    <t>义乌微创医院靠谱吗真实经历</t>
+  </si>
+  <si>
+    <t>义乌微创医院到底好不好</t>
+  </si>
+  <si>
+    <t>义乌微创医院情况怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院收费情况如何</t>
+  </si>
+  <si>
+    <t>义乌微创医院费用贵不贵</t>
+  </si>
+  <si>
+    <t>义乌微创医院价格高不高</t>
+  </si>
+  <si>
+    <t>义乌微创医院收费合理吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院检查费用怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院医生靠谱吗知乎</t>
+  </si>
+  <si>
+    <t>义乌微创医院医生评价如何</t>
+  </si>
+  <si>
+    <t>义乌微创医院医生水平怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院医生好不好</t>
+  </si>
+  <si>
+    <t>义乌微创医院技术靠谱吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院服务好不好</t>
+  </si>
+  <si>
+    <t>义乌微创医院体验怎么样知乎</t>
+  </si>
+  <si>
+    <t>义乌微创医院环境好不好</t>
+  </si>
+  <si>
+    <t>义乌微创医院就诊体验如何</t>
+  </si>
+  <si>
+    <t>义乌微创医院看病流程复杂吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院是不是正规的吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院是不是私立医院</t>
+  </si>
+  <si>
+    <t>义乌微创医院资质怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院靠谱吗安全吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院看妇科靠谱吗</t>
+  </si>
+  <si>
+    <t>义乌微创医院妇科评价怎么样</t>
+  </si>
+  <si>
+    <t>义乌微创医院妇科好不好</t>
+  </si>
+  <si>
+    <t>义乌微创医院妇科怎么样真实情况</t>
+  </si>
+  <si>
+    <t>义乌哪家妇科医院比较靠谱</t>
+  </si>
+  <si>
+    <t>义乌妇科医院哪家评价好</t>
+  </si>
+  <si>
+    <t>义乌妇科医院哪个好一点</t>
+  </si>
+  <si>
+    <t>义乌看妇科医院怎么选</t>
+  </si>
+  <si>
+    <t>义乌妇科医院收费情况</t>
+  </si>
+  <si>
+    <t>私立妇科医院靠谱吗义乌</t>
   </si>
   <si>
     <t>义乌私立医院靠谱吗</t>
   </si>
   <si>
-    <t>私立医院看皮肤科可靠吗</t>
-  </si>
-  <si>
-    <t>私立医院和公立医院差别皮肤科</t>
-  </si>
-  <si>
-    <t>私立医院值不值得去皮肤科</t>
-  </si>
-  <si>
-    <t>义乌义城手术靠谱吗皮肤科</t>
-  </si>
-  <si>
-    <t>义乌义城治疗皮肤科安全吗</t>
-  </si>
-  <si>
-    <t>义城医院和普通医院区别</t>
-  </si>
-  <si>
-    <t>义乌义城治疗好不好妇科</t>
-  </si>
-  <si>
-    <t>义乌义城医院值不值得去</t>
+    <t>私立医院看妇科可靠吗</t>
+  </si>
+  <si>
+    <t>私立医院和公立医院差别妇科</t>
+  </si>
+  <si>
+    <t>私立医院值不值得去妇科</t>
+  </si>
+  <si>
+    <t>义乌微创手术靠谱吗妇科</t>
+  </si>
+  <si>
+    <t>义乌微创治疗妇科安全吗</t>
+  </si>
+  <si>
+    <t>微创医院和普通医院区别</t>
+  </si>
+  <si>
+    <t>义乌微创治疗好不好妇科</t>
+  </si>
+  <si>
+    <t>义乌微创医院值不值得去</t>
   </si>
 </sst>
 </file>
